--- a/vehicle_inspection_forms/050_vehicle_check_engine_light_issue_report_form--vehicle_inspection_forms.xlsx
+++ b/vehicle_inspection_forms/050_vehicle_check_engine_light_issue_report_form--vehicle_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'toyota'}</t>
+          <t>toyota</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Toyota'}</t>
+          <t>Toyota</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'honda'}</t>
+          <t>honda</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Honda'}</t>
+          <t>Honda</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_51,_'label':_4.0}</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 51, 'label': 4.0}</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_52,_'label':_4.3}</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 52, 'label': 4.3}</t>
+          <t>4.3</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_52,_'label':_6.0}</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 52, 'label': 6.0}</t>
+          <t>6.0</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_61,_'label':_'automatic'}</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 61, 'label': 'Automatic'}</t>
+          <t>Automatic</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_62,_'label':_'manual'}</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 62, 'label': 'Manual'}</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_62,_'label':_'cvt'}</t>
+          <t>cvt</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 62, 'label': 'CVT'}</t>
+          <t>CVT</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_63,_'label':_'continuously_variable'}</t>
+          <t>continuously_variable</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 63, 'label': 'Continuously variable'}</t>
+          <t>Continuously variable</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_71,_'label':_'no_issue'}</t>
+          <t>no_issue</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 71, 'label': 'No issue'}</t>
+          <t>No issue</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_72,_'label':_'low_engine_oil_level'}</t>
+          <t>low_engine_oil_level</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 72, 'label': 'Low engine oil level'}</t>
+          <t>Low engine oil level</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_72,_'label':_'high_engine_oil_level'}</t>
+          <t>high_engine_oil_level</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 72, 'label': 'High engine oil level'}</t>
+          <t>High engine oil level</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_73,_'label':_'other_engine_issues'}</t>
+          <t>other_engine_issues</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 73, 'label': 'Other engine issues'}</t>
+          <t>Other engine issues</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_81,_'label':_'low_fuel'}</t>
+          <t>low_fuel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 81, 'label': 'Low fuel'}</t>
+          <t>Low fuel</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_82,_'label':_'high_fuel'}</t>
+          <t>high_fuel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 82, 'label': 'High fuel'}</t>
+          <t>High fuel</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_83,_'label':_'other_fuel_issues'}</t>
+          <t>other_fuel_issues</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 83, 'label': 'Other fuel issues'}</t>
+          <t>Other fuel issues</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_101,_'label':_'regular'}</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 101, 'label': 'Regular'}</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_102,_'label':_'premium'}</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 102, 'label': 'Premium'}</t>
+          <t>Premium</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_102,_'label':_'synthetic'}</t>
+          <t>synthetic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 102, 'label': 'Synthetic'}</t>
+          <t>Synthetic</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_121,_'label':_'gallons'}</t>
+          <t>gallons</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 121, 'label': 'Gallons'}</t>
+          <t>Gallons</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_122,_'label':_'liters'}</t>
+          <t>liters</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 122, 'label': 'Liters'}</t>
+          <t>Liters</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_122,_'label':_'other_units'}</t>
+          <t>other_units</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 122, 'label': 'Other units'}</t>
+          <t>Other units</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_141,_'label':_'miles'}</t>
+          <t>miles</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 141, 'label': 'Miles'}</t>
+          <t>Miles</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_142,_'label':_'kilometers'}</t>
+          <t>kilometers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 142, 'label': 'Kilometers'}</t>
+          <t>Kilometers</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_151,_'label':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 151, 'label': 'Clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_152,_'label':_'dirty'}</t>
+          <t>dirty</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 152, 'label': 'Dirty'}</t>
+          <t>Dirty</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_152,_'label':_'filtered'}</t>
+          <t>filtered</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 152, 'label': 'Filtered'}</t>
+          <t>Filtered</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_161,_'label':_'disposable'}</t>
+          <t>disposable</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 161, 'label': 'Disposable'}</t>
+          <t>Disposable</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_162,_'label':_'cartridge'}</t>
+          <t>cartridge</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 162, 'label': 'Cartridge'}</t>
+          <t>Cartridge</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_171,_'label':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 171, 'label': 'Clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_172,_'label':_'dirty'}</t>
+          <t>dirty</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 172, 'label': 'Dirty'}</t>
+          <t>Dirty</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_172,_'label':_'filtered'}</t>
+          <t>filtered</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 172, 'label': 'Filtered'}</t>
+          <t>Filtered</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_181,_'label':_'disposable'}</t>
+          <t>disposable</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 181, 'label': 'Disposable'}</t>
+          <t>Disposable</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_182,_'label':_'cartridge'}</t>
+          <t>cartridge</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 182, 'label': 'Cartridge'}</t>
+          <t>Cartridge</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_201,_'label':_'synthetic'}</t>
+          <t>synthetic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 201, 'label': 'Synthetic'}</t>
+          <t>Synthetic</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_202,_'label':_'regular'}</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 202, 'label': 'Regular'}</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_202,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 202, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_221,_'label':_'gallons'}</t>
+          <t>gallons</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 221, 'label': 'Gallons'}</t>
+          <t>Gallons</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_222,_'label':_'liters'}</t>
+          <t>liters</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 222, 'label': 'Liters'}</t>
+          <t>Liters</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_222,_'label':_'other_units'}</t>
+          <t>other_units</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 222, 'label': 'Other units'}</t>
+          <t>Other units</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_231,_'label':_'automatic'}</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 231, 'label': 'Automatic'}</t>
+          <t>Automatic</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_232,_'label':_'manual'}</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 232, 'label': 'Manual'}</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_232,_'label':_'continuously_variable'}</t>
+          <t>continuously_variable</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 232, 'label': 'Continuously variable'}</t>
+          <t>Continuously variable</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_241,_'label':_'disposable'}</t>
+          <t>disposable</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 241, 'label': 'Disposable'}</t>
+          <t>Disposable</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_242,_'label':_'cartridge'}</t>
+          <t>cartridge</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 242, 'label': 'Cartridge'}</t>
+          <t>Cartridge</t>
         </is>
       </c>
     </row>
